--- a/artfynd/A 6249-2024 artfynd.xlsx
+++ b/artfynd/A 6249-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6249-2024 artfynd.xlsx
+++ b/artfynd/A 6249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96860947</v>
+        <v>96860926</v>
       </c>
       <c r="B2" t="n">
-        <v>57935</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -714,14 +709,14 @@
       <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västerås, Vstm</t>
+          <t>Eriksbo Plantskola, Västerås, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586654</v>
+        <v>586796</v>
       </c>
       <c r="R2" t="n">
-        <v>6601221</v>
+        <v>6601268</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,6 +772,212 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>96860947</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västerås, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>586654</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6601221</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västerås-Barkarö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>116896241</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Barkaröby, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>586481</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6601325</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västerås-Barkarö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>ALN0059 Skogskällan NVI Västerås 2024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6249-2024 artfynd.xlsx
+++ b/artfynd/A 6249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860926</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860947</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
           <t>ALN0059 Skogskällan NVI Västerås 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116896241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>